--- a/InputData/elec/WUbPPT/Water Use by Power Plant Type.xlsx
+++ b/InputData/elec/WUbPPT/Water Use by Power Plant Type.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26731"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Dropbox (Energy Innovation)\EPS Versions\eps-1.5.0-us-wipI - units progress\InputData\elec\WUbPPT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\elec\WUbPPT\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CABAB2E8-C7B5-485C-A73C-3C2E68CFD24C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13500"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -20,17 +21,27 @@
     <sheet name="WUbPPT-withdrawals" sheetId="6" r:id="rId6"/>
     <sheet name="WUbPPT-consumption" sheetId="8" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="96">
   <si>
     <t>Reference,date=2018-28-11T14:16:43-08:00</t>
   </si>
@@ -221,9 +232,6 @@
     <t>hard coal</t>
   </si>
   <si>
-    <t>natural gas nonpeaker</t>
-  </si>
-  <si>
     <t>onshore wind</t>
   </si>
   <si>
@@ -290,17 +298,44 @@
     <t>municipal solid waste</t>
   </si>
   <si>
-    <t>Water withdrawals (liters/(MW*hour))</t>
-  </si>
-  <si>
-    <t>Water consumption (liters/(MW*hour))</t>
+    <t>natural gas steam turbine</t>
+  </si>
+  <si>
+    <t>natural gas combined cycle</t>
+  </si>
+  <si>
+    <t>Unit: liters/(MW*hour)</t>
+  </si>
+  <si>
+    <t>Water demand</t>
+  </si>
+  <si>
+    <t>hard coal w CCS</t>
+  </si>
+  <si>
+    <t>natural gas combined cycle w CCS</t>
+  </si>
+  <si>
+    <t>biomass w CCS</t>
+  </si>
+  <si>
+    <t>lignite w CCS</t>
+  </si>
+  <si>
+    <t>small modular reactor</t>
+  </si>
+  <si>
+    <t>hydrogen combustion turbine</t>
+  </si>
+  <si>
+    <t>hydrogen combined cycle</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -320,6 +355,29 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -352,7 +410,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -373,6 +431,11 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -654,19 +717,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B29"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>56</v>
       </c>
@@ -674,135 +737,135 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" s="7">
         <v>2018</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" s="8" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26">
         <f>10^12</f>
         <v>1000000000000</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>277777777.77777702</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B6" r:id="rId1"/>
+    <hyperlink ref="B6" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Z25"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="18.3984375" customWidth="1"/>
-    <col min="4" max="4" width="27.3984375" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="27.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>38</v>
       </c>
@@ -882,7 +945,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -962,7 +1025,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -1042,7 +1105,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -1122,7 +1185,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -1202,7 +1265,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -1282,7 +1345,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>0</v>
       </c>
@@ -1362,7 +1425,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>0</v>
       </c>
@@ -1442,7 +1505,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -1522,7 +1585,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>0</v>
       </c>
@@ -1602,7 +1665,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>0</v>
       </c>
@@ -1682,7 +1745,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>0</v>
       </c>
@@ -1762,7 +1825,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>0</v>
       </c>
@@ -1842,7 +1905,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>0</v>
       </c>
@@ -1922,7 +1985,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>0</v>
       </c>
@@ -2002,7 +2065,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>0</v>
       </c>
@@ -2082,7 +2145,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>0</v>
       </c>
@@ -2162,7 +2225,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>0</v>
       </c>
@@ -2242,7 +2305,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>0</v>
       </c>
@@ -2322,7 +2385,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>0</v>
       </c>
@@ -2402,7 +2465,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>0</v>
       </c>
@@ -2482,7 +2545,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>0</v>
       </c>
@@ -2562,7 +2625,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>0</v>
       </c>
@@ -2642,7 +2705,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>0</v>
       </c>
@@ -2722,7 +2785,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>0</v>
       </c>
@@ -2808,17 +2871,17 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AB16"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" customWidth="1"/>
-    <col min="3" max="3" width="12.73046875" customWidth="1"/>
-    <col min="4" max="4" width="15.59765625" customWidth="1"/>
-    <col min="5" max="5" width="29.265625" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
+    <col min="5" max="5" width="29.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>38</v>
       </c>
@@ -2904,7 +2967,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -2990,7 +3053,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -3076,7 +3139,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -3162,7 +3225,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -3248,7 +3311,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -3334,7 +3397,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>0</v>
       </c>
@@ -3420,7 +3483,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>0</v>
       </c>
@@ -3506,7 +3569,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -3592,7 +3655,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>0</v>
       </c>
@@ -3678,7 +3741,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>0</v>
       </c>
@@ -3764,7 +3827,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>0</v>
       </c>
@@ -3850,7 +3913,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>0</v>
       </c>
@@ -3936,7 +3999,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>0</v>
       </c>
@@ -4022,7 +4085,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>0</v>
       </c>
@@ -4108,7 +4171,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>0</v>
       </c>
@@ -4200,17 +4263,17 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AB17"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="14.59765625" customWidth="1"/>
-    <col min="4" max="4" width="17.1328125" customWidth="1"/>
-    <col min="5" max="5" width="27.73046875" customWidth="1"/>
-    <col min="6" max="6" width="18.86328125" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" customWidth="1"/>
+    <col min="4" max="4" width="17.140625" customWidth="1"/>
+    <col min="5" max="5" width="27.7109375" customWidth="1"/>
+    <col min="6" max="6" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>38</v>
       </c>
@@ -4296,7 +4359,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -4382,7 +4445,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -4468,7 +4531,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -4554,7 +4617,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -4640,7 +4703,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -4726,7 +4789,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>0</v>
       </c>
@@ -4812,7 +4875,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>0</v>
       </c>
@@ -4898,7 +4961,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -4984,7 +5047,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>0</v>
       </c>
@@ -5070,7 +5133,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>0</v>
       </c>
@@ -5156,7 +5219,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>0</v>
       </c>
@@ -5242,7 +5305,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>0</v>
       </c>
@@ -5328,7 +5391,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>0</v>
       </c>
@@ -5414,7 +5477,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>0</v>
       </c>
@@ -5500,7 +5563,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>0</v>
       </c>
@@ -5586,7 +5649,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>0</v>
       </c>
@@ -5679,19 +5742,19 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H17"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="2" width="18.59765625" customWidth="1"/>
-    <col min="3" max="3" width="27.265625" customWidth="1"/>
-    <col min="4" max="4" width="27.3984375" customWidth="1"/>
-    <col min="5" max="5" width="29.265625" customWidth="1"/>
-    <col min="6" max="8" width="28.59765625" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" customWidth="1"/>
+    <col min="3" max="3" width="27.28515625" customWidth="1"/>
+    <col min="4" max="4" width="27.42578125" customWidth="1"/>
+    <col min="5" max="5" width="29.28515625" customWidth="1"/>
+    <col min="6" max="8" width="28.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>41</v>
       </c>
@@ -5717,7 +5780,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -5750,7 +5813,7 @@
         <v/>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -5783,7 +5846,7 @@
         <v>971.73432153190504</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -5816,7 +5879,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -5849,7 +5912,7 @@
         <v>1960.1218806510001</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -5882,7 +5945,7 @@
         <v>620.64013917559782</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -5915,7 +5978,7 @@
         <v>745.03641899418494</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -5948,7 +6011,7 @@
         <v>4930.3337614825323</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -5977,7 +6040,7 @@
         <v>16999.982182329317</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -6010,7 +6073,7 @@
         <v>2226.6884419345611</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -6043,7 +6106,7 @@
         <v>1684.774202794702</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -6076,7 +6139,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -6109,7 +6172,7 @@
         <v>1183.8566612430841</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -6142,7 +6205,7 @@
         <v>2103.5281074696754</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -6175,7 +6238,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -6208,7 +6271,7 @@
         <v>20.000187272534593</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -6247,23 +6310,26 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
-    <tabColor theme="8" tint="-0.249977111117893"/>
+    <tabColor theme="8" tint="-0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:B25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.265625" customWidth="1"/>
-    <col min="2" max="2" width="18.265625" customWidth="1"/>
+    <col min="1" max="1" width="26.5703125" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>87</v>
+      </c>
       <c r="B1" s="10" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>62</v>
       </c>
@@ -6272,137 +6338,449 @@
         <v>54577.83755331373</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="B3" s="6">
+        <f>'2015 Consolidated Data'!G7</f>
+        <v>30331.387156235895</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" s="6">
         <f>'2015 Consolidated Data'!G6</f>
         <v>4159.9245358989992</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B5" s="6">
         <f>'2015 Consolidated Data'!G11</f>
         <v>63249.562164099065</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B6" s="6">
         <f>'2015 Consolidated Data'!G9</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>64</v>
       </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>65</v>
-      </c>
-      <c r="B7" s="6">
+      <c r="B8" s="6">
         <f>'2015 Consolidated Data'!G16</f>
         <v>20.000187272534593</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>66</v>
-      </c>
-      <c r="B8" s="6">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" s="6">
         <f>'2015 Consolidated Data'!G14</f>
         <v>2103.5281074696754</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B10" s="6">
         <f>'2015 Consolidated Data'!G3</f>
         <v>13890.685457654999</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B11" s="6">
         <f>'2015 Consolidated Data'!G8</f>
         <v>4930.3337614825323</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>67</v>
-      </c>
-      <c r="B11" s="6">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" s="6">
         <f>'2015 Consolidated Data'!G13</f>
         <v>23313.172724314474</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>68</v>
-      </c>
-      <c r="B12" s="6">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" s="6">
         <f>'2015 Consolidated Data'!G7</f>
         <v>30331.387156235895</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>69</v>
-      </c>
-      <c r="B13" s="6">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" s="6">
         <f>'2015 Consolidated Data'!G5</f>
         <v>54577.83755331373</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>69</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16" s="6">
+        <f>B12</f>
+        <v>23313.172724314474</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>83</v>
+      </c>
+      <c r="B17" s="6">
+        <f>B12</f>
+        <v>23313.172724314474</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B18" s="6">
+        <f>B10</f>
+        <v>13890.685457654999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" s="6">
+        <f>B2</f>
+        <v>54577.83755331373</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>90</v>
+      </c>
+      <c r="B20" s="6">
+        <f>B4</f>
+        <v>4159.9245358989992</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>91</v>
+      </c>
+      <c r="B21" s="6">
+        <f>B10</f>
+        <v>13890.685457654999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>92</v>
+      </c>
+      <c r="B22" s="6">
+        <f>B14</f>
+        <v>54577.83755331373</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B23" s="6">
+        <f>B5</f>
+        <v>63249.562164099065</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="B24" s="6">
+        <f>B13</f>
+        <v>30331.387156235895</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="B25" s="6">
+        <f>B4</f>
+        <v>4159.9245358989992</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <sheetPr>
+    <tabColor theme="8" tint="-0.499984740745262"/>
+  </sheetPr>
+  <dimension ref="A1:B25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="26.5703125" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" s="6">
+        <f>'2015 Consolidated Data'!H5</f>
+        <v>1960.1218806510001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" s="6">
+        <f>'2015 Consolidated Data'!H7</f>
+        <v>745.03641899418494</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" s="6">
+        <f>'2015 Consolidated Data'!H6</f>
+        <v>620.64013917559782</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="6">
+        <f>'2015 Consolidated Data'!H11</f>
+        <v>1684.774202794702</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="6">
+        <f>'2015 Consolidated Data'!H9</f>
+        <v>16999.982182329317</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" s="6">
+        <f>'2015 Consolidated Data'!H16</f>
+        <v>20.000187272534593</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" s="6">
+        <f>'2015 Consolidated Data'!H14</f>
+        <v>2103.5281074696754</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="6">
+        <f>'2015 Consolidated Data'!H3</f>
+        <v>971.73432153190504</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="6">
+        <f>'2015 Consolidated Data'!H8</f>
+        <v>4930.3337614825323</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" s="6">
+        <f>'2015 Consolidated Data'!H13</f>
+        <v>1183.8566612430841</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" s="6">
+        <f>'2015 Consolidated Data'!H7</f>
+        <v>745.03641899418494</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>70</v>
-      </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+        <v>68</v>
+      </c>
+      <c r="B14" s="6">
+        <f>'2015 Consolidated Data'!H5</f>
+        <v>1960.1218806510001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>69</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16" s="6">
+        <f>B12</f>
+        <v>1183.8566612430841</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>83</v>
       </c>
-      <c r="B15" s="6">
-        <f>B11</f>
-        <v>23313.172724314474</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
+      <c r="B17" s="6">
+        <f>B12</f>
+        <v>1183.8566612430841</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="6">
-        <f>B11</f>
-        <v>23313.172724314474</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>85</v>
-      </c>
-      <c r="B17" s="6">
-        <f>B9</f>
-        <v>13890.685457654999</v>
+      <c r="B18" s="6">
+        <f>B10</f>
+        <v>971.73432153190504</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" s="6">
+        <f>B2</f>
+        <v>1960.1218806510001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>90</v>
+      </c>
+      <c r="B20" s="6">
+        <f>B4</f>
+        <v>620.64013917559782</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>91</v>
+      </c>
+      <c r="B21" s="6">
+        <f>B10</f>
+        <v>971.73432153190504</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>92</v>
+      </c>
+      <c r="B22" s="6">
+        <f>B14</f>
+        <v>1960.1218806510001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B23" s="6">
+        <f>B5</f>
+        <v>1684.774202794702</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="B24" s="6">
+        <f>B13</f>
+        <v>745.03641899418494</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="B25" s="6">
+        <f>B4</f>
+        <v>620.64013917559782</v>
       </c>
     </row>
   </sheetData>
@@ -6410,166 +6788,173 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor theme="8" tint="-0.249977111117893"/>
-  </sheetPr>
-  <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="24.265625" customWidth="1"/>
-    <col min="2" max="2" width="18.265625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="B1" s="10" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B2" s="6">
-        <f>'2015 Consolidated Data'!H5</f>
-        <v>1960.1218806510001</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B3" s="6">
-        <f>'2015 Consolidated Data'!H6</f>
-        <v>620.64013917559782</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="6">
-        <f>'2015 Consolidated Data'!H11</f>
-        <v>1684.774202794702</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="6">
-        <f>'2015 Consolidated Data'!H9</f>
-        <v>16999.982182329317</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>65</v>
-      </c>
-      <c r="B7" s="6">
-        <f>'2015 Consolidated Data'!H16</f>
-        <v>20.000187272534593</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>66</v>
-      </c>
-      <c r="B8" s="6">
-        <f>'2015 Consolidated Data'!H14</f>
-        <v>2103.5281074696754</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="6">
-        <f>'2015 Consolidated Data'!H3</f>
-        <v>971.73432153190504</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="6">
-        <f>'2015 Consolidated Data'!H8</f>
-        <v>4930.3337614825323</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>67</v>
-      </c>
-      <c r="B11" s="6">
-        <f>'2015 Consolidated Data'!H13</f>
-        <v>1183.8566612430841</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>68</v>
-      </c>
-      <c r="B12" s="6">
-        <f>'2015 Consolidated Data'!H7</f>
-        <v>745.03641899418494</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>69</v>
-      </c>
-      <c r="B13" s="6">
-        <f>'2015 Consolidated Data'!H5</f>
-        <v>1960.1218806510001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>70</v>
-      </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>83</v>
-      </c>
-      <c r="B15" s="6">
-        <f>B11</f>
-        <v>1183.8566612430841</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>84</v>
-      </c>
-      <c r="B16" s="6">
-        <f>B11</f>
-        <v>1183.8566612430841</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>85</v>
-      </c>
-      <c r="B17" s="6">
-        <f>B9</f>
-        <v>971.73432153190504</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002041A8AB53924247A2770D65450F5227" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="90fff4f083191fe75a03dbd50c7739fc">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1659011e-6b88-4225-9a61-aaf33aaf19e8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7fee88694a371868130ae0617c69143c" ns2:_="">
+    <xsd:import namespace="1659011e-6b88-4225-9a61-aaf33aaf19e8"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="1659011e-6b88-4225-9a61-aaf33aaf19e8" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C44ECE6-9BF4-4133-B9A2-F1947C3F4CF7}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{092F7F1C-D982-48E2-9C70-A1505BB8D215}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E74B3B9F-1464-4314-90B2-57038849AAA0}"/>
 </file>